--- a/GUA/IPPU/A2_Structure_Lists.xlsx
+++ b/GUA/IPPU/A2_Structure_Lists.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="58">
   <si>
     <t>Year</t>
   </si>
@@ -43,13 +43,94 @@
     <t>RAW_MAT_CEM</t>
   </si>
   <si>
+    <t>IMP_STOR</t>
+  </si>
+  <si>
+    <t>LIME_CAL_PROD</t>
+  </si>
+  <si>
+    <t>LIME_DOL_PROD</t>
+  </si>
+  <si>
+    <t>GLASS_PROD</t>
+  </si>
+  <si>
+    <t>CARBONATE_CERAMICS</t>
+  </si>
+  <si>
+    <t>CARBONATE_ASH</t>
+  </si>
+  <si>
+    <t>IRON_STEEL</t>
+  </si>
+  <si>
+    <t>PROD_FERRO</t>
+  </si>
+  <si>
+    <t>LUBRI_OILS</t>
+  </si>
+  <si>
+    <t>PARAFFIN</t>
+  </si>
+  <si>
+    <t>REFR_AC_HFC32</t>
+  </si>
+  <si>
+    <t>REFR_AC_HFC125</t>
+  </si>
+  <si>
+    <t>REFR_AC_HFC134a</t>
+  </si>
+  <si>
+    <t>REFR_AC_HFC143a</t>
+  </si>
+  <si>
     <t>PROD_CLK_TRAD</t>
   </si>
   <si>
     <t>PROD_CEM</t>
   </si>
   <si>
-    <t>T5CEM_PRODCEM_PROD</t>
+    <t>T5CEM_PRODIND</t>
+  </si>
+  <si>
+    <t>T5LIME_CAL_PRODIPPU</t>
+  </si>
+  <si>
+    <t>T5LIME_DOL_PRODIPPU</t>
+  </si>
+  <si>
+    <t>T5GLASS_PRODIPPU</t>
+  </si>
+  <si>
+    <t>T5CARBONATE_CERAMICSIPPU</t>
+  </si>
+  <si>
+    <t>T5CARBONATE_ASHIPPU</t>
+  </si>
+  <si>
+    <t>T5IRON_STEELIPPU</t>
+  </si>
+  <si>
+    <t>T5PROD_FERROIPPU</t>
+  </si>
+  <si>
+    <t>T5LUBRI_OILSIPPU</t>
+  </si>
+  <si>
+    <t>T5PARAFFINIPPU</t>
+  </si>
+  <si>
+    <t>T5REFR_AC_HFC32IPPU</t>
+  </si>
+  <si>
+    <t>T5REFR_AC_HFC125IPPU</t>
+  </si>
+  <si>
+    <t>T5REFR_AC_HFC134aIPPU</t>
+  </si>
+  <si>
+    <t>T5REFR_AC_HFC143aIPPU</t>
   </si>
   <si>
     <t>All</t>
@@ -61,34 +142,49 @@
     <t>CEM_PROD</t>
   </si>
   <si>
-    <t>E5_CEM_PRODCEM_PROD</t>
-  </si>
-  <si>
-    <t>CO2e_CERAS</t>
-  </si>
-  <si>
-    <t>CO2e_HIER</t>
-  </si>
-  <si>
-    <t>CO2e_FERRO</t>
-  </si>
-  <si>
-    <t>CO2e_RAC</t>
-  </si>
-  <si>
-    <t>CO2e_CARBONATO</t>
-  </si>
-  <si>
-    <t>CO2e_VID</t>
-  </si>
-  <si>
-    <t>CO2e_CAL</t>
-  </si>
-  <si>
-    <t>CO2e_CEM</t>
-  </si>
-  <si>
-    <t>CO2e_LUB</t>
+    <t>E5INDCEM_PROD</t>
+  </si>
+  <si>
+    <t>E5IPPULIME_CAL_PROD</t>
+  </si>
+  <si>
+    <t>E5IPPULIME_DOL_PROD</t>
+  </si>
+  <si>
+    <t>E5IPPUGLASS_PROD</t>
+  </si>
+  <si>
+    <t>E5IPPUCARBONATE_CERAMICS</t>
+  </si>
+  <si>
+    <t>E5IPPUCARBONATE_ASH</t>
+  </si>
+  <si>
+    <t>E5IPPUIRON_STEEL</t>
+  </si>
+  <si>
+    <t>E5IPPUPROD_FERRO</t>
+  </si>
+  <si>
+    <t>E5IPPULUBRI_OILS</t>
+  </si>
+  <si>
+    <t>E5IPPUPARAFFIN</t>
+  </si>
+  <si>
+    <t>E5IPPUREFR_AC_HFC32</t>
+  </si>
+  <si>
+    <t>E5IPPUREFR_AC_HFC125</t>
+  </si>
+  <si>
+    <t>E5IPPUREFR_AC_HFC134a</t>
+  </si>
+  <si>
+    <t>E5IPPUREFR_AC_HFC143a</t>
+  </si>
+  <si>
+    <t>CO2e_IPPU</t>
   </si>
   <si>
     <t>GUA</t>
@@ -483,19 +579,19 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s">
         <v>7</v>
       </c>
       <c r="E2" t="s">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="F2">
         <v>1</v>
       </c>
       <c r="G2" t="s">
-        <v>25</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -508,9 +604,6 @@
       <c r="D3" t="s">
         <v>8</v>
       </c>
-      <c r="E3" t="s">
-        <v>17</v>
-      </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
@@ -520,10 +613,7 @@
         <v>9</v>
       </c>
       <c r="D4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -534,10 +624,7 @@
         <v>10</v>
       </c>
       <c r="D5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -548,160 +635,304 @@
         <v>11</v>
       </c>
       <c r="D6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E6" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
         <v>2023</v>
       </c>
-      <c r="E7" t="s">
-        <v>21</v>
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
         <v>2024</v>
       </c>
-      <c r="E8" t="s">
-        <v>22</v>
+      <c r="B8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
         <v>2025</v>
       </c>
-      <c r="E9" t="s">
-        <v>23</v>
+      <c r="B9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
         <v>2026</v>
       </c>
-      <c r="E10" t="s">
-        <v>24</v>
+      <c r="B10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
         <v>2027</v>
       </c>
+      <c r="B11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
         <v>2028</v>
       </c>
+      <c r="B12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D12" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
         <v>2029</v>
       </c>
+      <c r="B13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D13" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
         <v>2030</v>
       </c>
+      <c r="B14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
         <v>2031</v>
       </c>
+      <c r="B15" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
         <v>2032</v>
       </c>
-    </row>
-    <row r="17" spans="1:1">
+      <c r="B16" t="s">
+        <v>21</v>
+      </c>
+      <c r="D16" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
       <c r="A17">
         <v>2033</v>
       </c>
-    </row>
-    <row r="18" spans="1:1">
+      <c r="B17" t="s">
+        <v>22</v>
+      </c>
+      <c r="D17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
       <c r="A18">
         <v>2034</v>
       </c>
-    </row>
-    <row r="19" spans="1:1">
+      <c r="B18" t="s">
+        <v>23</v>
+      </c>
+      <c r="D18" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
       <c r="A19">
         <v>2035</v>
       </c>
-    </row>
-    <row r="20" spans="1:1">
+      <c r="B19" t="s">
+        <v>24</v>
+      </c>
+      <c r="D19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
       <c r="A20">
         <v>2036</v>
       </c>
-    </row>
-    <row r="21" spans="1:1">
+      <c r="B20" t="s">
+        <v>25</v>
+      </c>
+      <c r="D20" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
       <c r="A21">
         <v>2037</v>
       </c>
-    </row>
-    <row r="22" spans="1:1">
+      <c r="B21" t="s">
+        <v>26</v>
+      </c>
+      <c r="D21" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
       <c r="A22">
         <v>2038</v>
       </c>
-    </row>
-    <row r="23" spans="1:1">
+      <c r="B22" t="s">
+        <v>27</v>
+      </c>
+      <c r="D22" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
       <c r="A23">
         <v>2039</v>
       </c>
-    </row>
-    <row r="24" spans="1:1">
+      <c r="B23" t="s">
+        <v>28</v>
+      </c>
+      <c r="D23" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
       <c r="A24">
         <v>2040</v>
       </c>
-    </row>
-    <row r="25" spans="1:1">
+      <c r="B24" t="s">
+        <v>29</v>
+      </c>
+      <c r="D24" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
       <c r="A25">
         <v>2041</v>
       </c>
-    </row>
-    <row r="26" spans="1:1">
+      <c r="B25" t="s">
+        <v>30</v>
+      </c>
+      <c r="D25" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
       <c r="A26">
         <v>2042</v>
       </c>
-    </row>
-    <row r="27" spans="1:1">
+      <c r="B26" t="s">
+        <v>31</v>
+      </c>
+      <c r="D26" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
       <c r="A27">
         <v>2043</v>
       </c>
-    </row>
-    <row r="28" spans="1:1">
+      <c r="B27" t="s">
+        <v>32</v>
+      </c>
+      <c r="D27" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
       <c r="A28">
         <v>2044</v>
       </c>
-    </row>
-    <row r="29" spans="1:1">
+      <c r="B28" t="s">
+        <v>33</v>
+      </c>
+      <c r="D28" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
       <c r="A29">
         <v>2045</v>
       </c>
-    </row>
-    <row r="30" spans="1:1">
+      <c r="B29" t="s">
+        <v>34</v>
+      </c>
+      <c r="D29" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
       <c r="A30">
         <v>2046</v>
       </c>
-    </row>
-    <row r="31" spans="1:1">
+      <c r="B30" t="s">
+        <v>35</v>
+      </c>
+      <c r="D30" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
       <c r="A31">
         <v>2047</v>
       </c>
-    </row>
-    <row r="32" spans="1:1">
+      <c r="B31" t="s">
+        <v>36</v>
+      </c>
+      <c r="D31" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
       <c r="A32">
         <v>2048</v>
       </c>
-    </row>
-    <row r="33" spans="1:1">
+      <c r="B32" t="s">
+        <v>37</v>
+      </c>
+      <c r="D32" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
       <c r="A33">
         <v>2049</v>
       </c>
-    </row>
-    <row r="34" spans="1:1">
+      <c r="B33" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
       <c r="A34">
         <v>2050</v>
       </c>
@@ -709,258 +940,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101000360DE9767CDF0449BF75EAB371D3CB7" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="75cb9a07855af6ac97bd432464ca7c04">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a1fcbaaf-06d9-47c4-b3a2-beefbc45d784" xmlns:ns3="081a93ea-d517-42a5-a2b7-457060aa7471" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d1676634304aab9936f6a5a5f53c7423" ns2:_="" ns3:_="">
-    <xsd:import namespace="a1fcbaaf-06d9-47c4-b3a2-beefbc45d784"/>
-    <xsd:import namespace="081a93ea-d517-42a5-a2b7-457060aa7471"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="a1fcbaaf-06d9-47c4-b3a2-beefbc45d784" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="11" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="71f7bd95-1200-4052-9a4e-dfdf006e181b" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="12" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="13" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="14" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="15" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="16" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="19" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="20" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="21" nillable="true" ma:displayName="Location" ma:description="" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="081a93ea-d517-42a5-a2b7-457060aa7471" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a1fcbaaf-06d9-47c4-b3a2-beefbc45d784">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A472BF10-CF55-43D7-937B-16D0BFF0A66D}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CAE4BD2-FAAA-48B7-8DC6-78C60D35E206}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4F3B72A7-7220-4976-9CA5-F5015144D63A}"/>
 </file>